--- a/artfynd/A 11933-2025 artfynd.xlsx
+++ b/artfynd/A 11933-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56755171</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368454.2395588089</v>
+        <v>368454</v>
       </c>
       <c r="R2" t="n">
-        <v>6565595.796742504</v>
+        <v>6565596</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2013-07-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tove Adelsköld, Åsa Röstell, Gabriella Malmborg</t>
+          <t>Gabriella Malmborg, Åsa Röstell, Tove Adelsköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -813,12 +798,7 @@
         <v>56755172</v>
       </c>
       <c r="B3" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -859,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368475.0158707637</v>
+        <v>368475</v>
       </c>
       <c r="R3" t="n">
-        <v>6565602.765959754</v>
+        <v>6565603</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,19 +872,9 @@
           <t>2013-07-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -934,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tove Adelsköld, Åsa Röstell, Gabriella Malmborg</t>
+          <t>Gabriella Malmborg, Åsa Röstell, Tove Adelsköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,15 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68717793</v>
+        <v>56755173</v>
       </c>
       <c r="B4" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,26 +945,24 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fjäll, Vrm</t>
+          <t>Dysslan, väg S530, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>368464.9547584321</v>
+        <v>368514</v>
       </c>
       <c r="R4" t="n">
-        <v>6565593.888977486</v>
+        <v>6565811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,34 +987,19 @@
           <t>Kila</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>S-Säf-0295</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>2013-07-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-07-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5 stjälkar nordväst vägskälet och 13 stjälkar nordost vägskälet.</t>
+          <t>växer på västra sidan av vägen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,7 +1011,7 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>Vägkant</t>
         </is>
@@ -1071,15 +1019,389 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>John Rolander Borlid</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johanna Borlid, Gabriella Malmborg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>56755174</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dysslan, väg S530, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>368536</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6565809</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>växer på östra sidan av vägen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>John Rolander Borlid</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johanna Borlid, Gabriella Malmborg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>68717792</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dysslan, SO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>368527</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6565810</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>S-Säf-0296</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>9 stälkar ost vägen, 1 stjälk väst vägen.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johanna Borlid, Gabriella Malmborg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>68717793</v>
+      </c>
+      <c r="B7" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fjäll, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>368465</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6565594</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>S-Säf-0295</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>5 stjälkar nordväst vägskälet och 13 stjälkar nordost vägskälet.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Tove Adelsköld, Åsa Röstell, Gabriella Malmborg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 11933-2025 artfynd.xlsx
+++ b/artfynd/A 11933-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56755171</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56755172</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56755173</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56755174</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,6 +1304,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68717792</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1406,8 +1436,21 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68717793</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>